--- a/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9252612557</v>
+        <v>46157.93094018977</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93094018977</v>
+        <v>46157.93356062632</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93356062632</v>
+        <v>46157.93650453824</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93650453824</v>
+        <v>46158.28183917992</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28183917992</v>
+        <v>46158.29762184567</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29762184567</v>
+        <v>46158.29777881375</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29777881375</v>
+        <v>46158.33345368261</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33345368261</v>
+        <v>46158.37204094444</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37204094444</v>
+        <v>46158.37399670421</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
